--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
@@ -4228,7 +4228,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4268,6 +4268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4896,7 +4902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="8" applyBorder="1"/>
@@ -5381,6 +5387,17 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="0" borderId="0" xfId="0"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -9030,40 +9047,40 @@
       </c>
     </row>
     <row r="18" spans="1:34">
-      <c r="A18" s="87"/>
-      <c r="B18" s="81" t="str">
+      <c r="A18" s="180"/>
+      <c r="B18" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="81" t="inlineStr">
+      <c r="C18" s="178"/>
+      <c r="D18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-LOGENC-006</t>
         </is>
       </c>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81" t="inlineStr">
+      <c r="E18" s="177"/>
+      <c r="F18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-LOGENC-009</t>
         </is>
       </c>
-      <c r="G18" s="81" t="inlineStr">
+      <c r="G18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Log Encrypt</t>
         </is>
       </c>
-      <c r="H18" s="81" t="inlineStr">
+      <c r="H18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Encryption Procedure</t>
         </is>
       </c>
-      <c r="I18" s="81" t="inlineStr">
+      <c r="I18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Encryption procedure should be:
 (symmetric key differs between two encryption iterations)</t>
         </is>
       </c>
-      <c r="J18" s="81" t="inlineStr">
+      <c r="J18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. Logdog is enabled on the DUT
@@ -9071,12 +9088,12 @@
 4. A USB drive containing __diagSpecialFile and __getSnapshot is inserted into the HU USB port</t>
         </is>
       </c>
-      <c r="K18" s="81" t="inlineStr">
+      <c r="K18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L18" s="81" t="inlineStr">
+      <c r="L18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Decrypt the first encrypted pair on the host
 $ ./logdecrypt_Ver2.sh HUssss_YYYYMMDD_HHMMSS_XXXX.enc HUssss_YYYYMMDD_HHMMSS_XXXX_enckey.enc
@@ -9086,86 +9103,86 @@
 $ &lt;command provided by RD (X-m)&gt;</t>
         </is>
       </c>
-      <c r="M18" s="81" t="inlineStr">
+      <c r="M18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The logdecrypt_Ver2.sh tool creates the folder HUssss_YYYYMMDD_HHMMSS_XXXX on the host
 2. The logdecrypt_Ver2.sh tool creates the folder HUssss_YYYYMMDD_HHMMSS_XXXX on the host
 3. &lt;two log snapshots taken in separate iterations + comparison provided by RD (X-m)&gt;</t>
         </is>
       </c>
-      <c r="N18" s="81" t="inlineStr">
+      <c r="N18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
         </is>
       </c>
-      <c r="O18" s="81" t="inlineStr">
+      <c r="O18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P18" s="81" t="inlineStr">
+      <c r="P18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81" t="inlineStr">
+      <c r="Q18" s="177"/>
+      <c r="R18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S18" s="81" t="inlineStr">
+      <c r="S18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T18" s="81" t="inlineStr">
+      <c r="T18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U18" s="81" t="inlineStr">
+      <c r="U18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V18" s="81" t="inlineStr">
+      <c r="V18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W18" s="81" t="inlineStr">
+      <c r="W18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X18" s="83" t="inlineStr">
+      <c r="X18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y18" s="81" t="inlineStr">
+      <c r="Y18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z18" s="83" t="inlineStr">
+      <c r="Z18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA18" s="83" t="inlineStr">
+      <c r="AA18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="83" t="inlineStr">
+      <c r="AB18" s="177"/>
+      <c r="AC18" s="177"/>
+      <c r="AD18" s="177"/>
+      <c r="AE18" s="177"/>
+      <c r="AF18" s="177"/>
+      <c r="AG18" s="177"/>
+      <c r="AH18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-LOGENC-006 Requirement Description and Verification Criteria
 sibling axis: key uniqueness

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-001</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-002</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-003</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-005</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-007</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-008</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-009</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
